--- a/news_daily/2026-09-22.xlsx
+++ b/news_daily/2026-09-22.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1161,6 +1189,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1211,13 +1243,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1266,7 +1302,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>ed664f6928a140bb8e80fc7a5389dd9f</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>ee35c0a5a1eabe2b10ed79fc</t>
@@ -1287,7 +1327,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1331,6 +1375,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1493,6 +1549,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1663,6 +1723,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1713,13 +1777,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1768,7 +1836,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>7f008e57229c4525928c23566a502bf7</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>2e3cbf412e6b971f409ab631</t>
@@ -1789,7 +1861,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1833,6 +1909,18 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1873,7 +1961,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1883,13 +1971,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1929,7 +2021,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1938,7 +2030,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>c011730a15f745b8addec9569a85b937</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>cfb78cadb9c95baa99c80188</t>
@@ -1959,7 +2055,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -1995,6 +2095,22 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2045,13 +2161,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2100,7 +2220,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>abf29ab2ecee42809099d56ada0c02fa</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>e0fed90d886dafd33a7a6572</t>
@@ -2121,7 +2245,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -2165,6 +2293,18 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2215,13 +2355,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2270,7 +2414,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>8f5394e3189146e8ac157d4d8e75852c</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>143c6de813c9ecade1e5f544</t>
@@ -2291,7 +2439,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -2335,6 +2487,18 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2375,7 +2539,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2385,13 +2549,17 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2431,7 +2599,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2440,7 +2608,11 @@
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>ce0f0fbadacd4f46a2d22c6f53ff87f4</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>0fad036315354fe89194f745</t>
@@ -2461,7 +2633,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2497,176 +2673,220 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Mastercard Incorporated Common Stock</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>2026-09-22T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>SoFi Becomes First National Bank to Go Live with Stablecoin Settlement across Mastercard’s Global Payments Network</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>0.547</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNOGstbTlTOVlGX0pybGlDYkpPR0ZDT29EdGJpX3IzRktxYW4ycHJ2dW9aVnQzYW45ellVWG55TDhleG9qWTFSdjhic2pibVBWSkdiVmtIOVIyeThTczZiWjhRR3FueDRZSFpxZ2VsUEg5bjFILV9jSTMwUzZJZlI1MUZfa0U5dkthQ2FoWUVaMGVFUzJpYkpRbG9OUTRNaGxLd1d3NS1XMV90UDA3Q3VEblZmZ1VwMTZqSUJlUFM1OEItRzRvdmF6NXc4Ym04S1lKVmhNTmRya1ZwdEV0U1Y1dHRqeGhMRnEwcktUT1VPUDNlTXlkbzN2ZzFxdUpRVlVjQmNYSTVlOA?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>SoFi Investor Relations</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>d4bbaddc742f465ea19c4d759f1cf314</t>
+        </is>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>09eeeeb2809badc3bc8f1e53</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>5a26db207b76537c169ab2ca</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>0.547</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNOGstbTlTOVlGX0pybGlDYkpPR0ZDT29EdGJpX3IzRktxYW4ycHJ2dW9aVnQzYW45ellVWG55TDhleG9qWTFSdjhic2pibVBWSkdiVmtIOVIyeThTczZiWjhRR3FueDRZSFpxZ2VsUEg5bjFILV9jSTMwUzZJZlI1MUZfa0U5dkthQ2FoWUVaMGVFUzJpYkpRbG9OUTRNaGxLd1d3NS1XMV90UDA3Q3VEblZmZ1VwMTZqSUJlUFM1OEItRzRvdmF6NXc4Ym04S1lKVmhNTmRya1ZwdEV0U1Y1dHRqeGhMRnEwcktUT1VPUDNlTXlkbzN2ZzFxdUpRVlVjQmNYSTVlOA?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>SoFi Investor Relations</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>09eeeeb2809badc3bc8f1e53</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>5a26db207b76537c169ab2ca</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="BC12" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BG12" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2717,13 +2937,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2772,7 +2996,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>0d2431f5e410458888841bf071fcc8e5</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>45cd1b814114d1e9bad0217b</t>
@@ -2793,7 +3021,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -2837,9 +3069,21 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2850,7 +3094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2913,6 +3157,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3214,6 +3462,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -3386,6 +3654,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3548,6 +3820,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3598,13 +3874,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -3653,7 +3933,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>ed664f6928a140bb8e80fc7a5389dd9f</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>ee35c0a5a1eabe2b10ed79fc</t>
@@ -3674,7 +3958,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -3718,6 +4006,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3880,6 +4180,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4050,6 +4354,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4100,13 +4408,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -4155,7 +4467,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>7f008e57229c4525928c23566a502bf7</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>2e3cbf412e6b971f409ab631</t>
@@ -4176,7 +4492,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -4220,6 +4540,18 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4260,7 +4592,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -4270,13 +4602,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -4316,7 +4652,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -4325,7 +4661,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>c011730a15f745b8addec9569a85b937</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>cfb78cadb9c95baa99c80188</t>
@@ -4346,7 +4686,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -4382,6 +4726,22 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -4432,13 +4792,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -4487,7 +4851,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>abf29ab2ecee42809099d56ada0c02fa</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>e0fed90d886dafd33a7a6572</t>
@@ -4508,7 +4876,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -4552,6 +4924,18 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4602,13 +4986,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -4657,7 +5045,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>8f5394e3189146e8ac157d4d8e75852c</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>143c6de813c9ecade1e5f544</t>
@@ -4678,7 +5070,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -4722,6 +5118,18 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4762,7 +5170,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -4772,13 +5180,17 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -4818,7 +5230,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -4827,7 +5239,11 @@
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>ce0f0fbadacd4f46a2d22c6f53ff87f4</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>0fad036315354fe89194f745</t>
@@ -4848,7 +5264,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -4884,6 +5304,22 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4898,12 +5334,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated Common Stock</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -4913,7 +5349,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>SoFi Becomes First National Bank to Go Live with Stablecoin Settlement across Mastercard’s Global Payments Network</t>
+          <t>DoorDash Agrees to $131.5 Million Settlement for Shortchanging Workers</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4934,13 +5370,17 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -4950,7 +5390,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>'-0.017</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr"/>
@@ -4964,12 +5404,12 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNOGstbTlTOVlGX0pybGlDYkpPR0ZDT29EdGJpX3IzRktxYW4ycHJ2dW9aVnQzYW45ellVWG55TDhleG9qWTFSdjhic2pibVBWSkdiVmtIOVIyeThTczZiWjhRR3FueDRZSFpxZ2VsUEg5bjFILV9jSTMwUzZJZlI1MUZfa0U5dkthQ2FoWUVaMGVFUzJpYkpRbG9OUTRNaGxLd1d3NS1XMV90UDA3Q3VEblZmZ1VwMTZqSUJlUFM1OEItRzRvdmF6NXc4Ym04S1lKVmhNTmRya1ZwdEV0U1Y1dHRqeGhMRnEwcktUT1VPUDNlTXlkbzN2ZzFxdUpRVlVjQmNYSTVlOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQX1lPRUYwa2hCaU56ZzNBaUZvQ0hvTHNONEx0OWxSdnQwTXRDd2dOeWZXbWl2TkhvWjNaYWE2Q2FQb0QwRy1LZk41MUktLW5ZMVlVRVBhUjR4X1Q2M3N0T1BNdzhLWmNXNk05RXpYQ1FmVVdJQTlDSFZuX21SNTNnLVNjYWt1VTJ6dkhvaDNR?oc=5</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>SoFi Investor Relations</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr"/>
@@ -4989,15 +5429,19 @@
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>0d2431f5e410458888841bf071fcc8e5</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>09eeeeb2809badc3bc8f1e53</t>
+          <t>45cd1b814114d1e9bad0217b</t>
         </is>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>5a26db207b76537c169ab2ca</t>
+          <t>e43fd33fff45d35320eff26a</t>
         </is>
       </c>
       <c r="AE12" s="3" t="inlineStr"/>
@@ -5010,7 +5454,11 @@
       <c r="AL12" s="3" t="inlineStr"/>
       <c r="AM12" s="3" t="inlineStr"/>
       <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="3" t="inlineStr"/>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr"/>
@@ -5020,7 +5468,7 @@
       <c r="AV12" s="3" t="inlineStr"/>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr"/>
@@ -5029,7 +5477,7 @@
       <c r="BA12" s="3" t="inlineStr"/>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="BC12" s="3" t="inlineStr">
@@ -5040,12 +5488,12 @@
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG12" s="3" t="inlineStr">
@@ -5054,179 +5502,21 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash, Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash Agrees to $131.5 Million Settlement for Shortchanging Workers</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>'-0.017</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQX1lPRUYwa2hCaU56ZzNBaUZvQ0hvTHNONEx0OWxSdnQwTXRDd2dOeWZXbWl2TkhvWjNaYWE2Q2FQb0QwRy1LZk41MUktLW5ZMVlVRVBhUjR4X1Q2M3N0T1BNdzhLWmNXNk05RXpYQ1FmVVdJQTlDSFZuX21SNTNnLVNjYWt1VTJ6dkhvaDNR?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t>The New York Times</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
-      <c r="AC13" s="3" t="inlineStr">
-        <is>
-          <t>45cd1b814114d1e9bad0217b</t>
-        </is>
-      </c>
-      <c r="AD13" s="3" t="inlineStr">
-        <is>
-          <t>e43fd33fff45d35320eff26a</t>
-        </is>
-      </c>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="BC13" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG13" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5237,7 +5527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5300,6 +5590,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5603,9 +5897,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5616,7 +5930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5679,6 +5993,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5982,9 +6300,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5995,7 +6333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6045,134 +6383,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -6182,46 +6520,80 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="4" t="inlineStr"/>
       <c r="Y2" s="4" t="inlineStr"/>
       <c r="Z2" s="4" t="inlineStr"/>
@@ -6230,12 +6602,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -6245,90 +6617,94 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -6338,94 +6714,94 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -6433,89 +6809,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-22.xlsx
+++ b/news_daily/2026-09-22.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,18 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -888,28 +880,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +945,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +954,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>212d4804b51d4196a439e994173b97a2</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>40545cfd797e34bd1fccb986</t>
@@ -979,7 +979,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1023,10 +1027,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1062,28 +1078,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1123,7 +1143,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1132,7 +1152,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>666c4c8f2cb746b19587e85eb3c53cb1</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>70ff7aa43f371daf788dc183</t>
@@ -1153,7 +1177,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1189,10 +1217,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1422,28 +1462,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1483,7 +1527,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1492,7 +1536,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>dba76ca673c94331bc20e8f1e4da6767</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>e674416ebd46d3b83ff64ddc</t>
@@ -1513,7 +1561,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1549,10 +1601,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1588,28 +1652,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1649,7 +1717,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1658,7 +1726,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>9131383469ee4913829b2958c2f5ed41</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>9877d4441ca0e3d1efc7e8cc</t>
@@ -1679,7 +1751,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1723,10 +1799,22 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2691,198 +2779,198 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mastercard Incorporated Common Stock</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-09-22T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>SoFi Becomes First National Bank to Go Live with Stablecoin Settlement across Mastercard’s Global Payments Network</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0.547</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNOGstbTlTOVlGX0pybGlDYkpPR0ZDT29EdGJpX3IzRktxYW4ycHJ2dW9aVnQzYW45ellVWG55TDhleG9qWTFSdjhic2pibVBWSkdiVmtIOVIyeThTczZiWjhRR3FueDRZSFpxZ2VsUEg5bjFILV9jSTMwUzZJZlI1MUZfa0U5dkthQ2FoWUVaMGVFUzJpYkpRbG9OUTRNaGxLd1d3NS1XMV90UDA3Q3VEblZmZ1VwMTZqSUJlUFM1OEItRzRvdmF6NXc4Ym04S1lKVmhNTmRya1ZwdEV0U1Y1dHRqeGhMRnEwcktUT1VPUDNlTXlkbzN2ZzFxdUpRVlVjQmNYSTVlOA?oc=5</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>SoFi Investor Relations</t>
         </is>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>d4bbaddc742f465ea19c4d759f1cf314</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>09eeeeb2809badc3bc8f1e53</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AD12" s="2" t="inlineStr">
         <is>
           <t>5a26db207b76537c169ab2ca</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="4" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr">
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr">
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL12" s="4" t="inlineStr">
+      <c r="BL12" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -3094,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL12"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3486,344 +3574,392 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>BALL</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Ball Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>DoorDash, Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2026-09-22T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Cubs expect Alex Bregman back for playoffs after foul ball to face</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>NYC Mayor Mamdani reaches record DoorDash settlement for underpaid workers</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>0.383</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPWXg3QnpvYVRxbXBDX1hjWmxFRjBiQUhvaVJ0VTBOaU9EdGFsT1ZtSzd2ZmNDN2pPempDTzhFTWM3YmRzekZvS1NfWk5DN1hVcUkzaFpuOGdZdXJPdVRIbkhORUdJNHdOcVZuUF81by1PYVNKSEprbmVxekwzWW85RzNBVW5SUENUUXIzOVhJYU96QnpkS2dyX19xUFRrUEJaLW42a09ES2dHUXJ4b1c3SFJYTUEwOFgyT2fSAb8BQVVfeXFMTnVzS0dCSlJxTHppRHk0NXNac3NneVZwTm14eVJvWElySlg5YlBmcjhQOGh0dHJwTVdaeGJOSFF1Z2VPUHE3VVd6SDViSy1ad00zcWVhbHY4S1FfVTJXNTc4Y3pQcDBDR2JYMnc0N1dNNE1Cc0x5MDhSSUZXeU5SMFM5cjZCcEFPdWZuc19nT3pUcEVQYUswdUFUQmhFbURhcV96LXF6Wk9zRjNTZlJjR0FvTXY0XzVCOEltZk53REE?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Al Jazeera</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>ed664f6928a140bb8e80fc7a5389dd9f</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>ee35c0a5a1eabe2b10ed79fc</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>401e1cc6f638d8d5292d8f4f</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.006</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQclV3bXdFRG0ycV9zZ2VtRU5kYVc1U2R3TElWR25nTFN0cDVKZVNvRGFJaWNIZW1fd3VGa3ZuN0tONmtqWXRSTXBEMVBNMnFKMGlzcjhOUnN0bnlSWGFBaUNkcnl2all2anp2T1dwNHB4WkJwRy1WdzhBemkwOGN0ZjNsUTBxcEs5VFBua25qTGh3Y2hWYmQxVnNKemNNNTVEdXQ3clZEeVJhT0F6akVIWjg0OA?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>ESPN</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>40545cfd797e34bd1fccb986</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>4345dc8aba2aa5cc10bd00f3</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>BALL</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Cooper Companies (The)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>DoorDash, Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-09-22T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Brewers COO Marti Wronski on playoff baseball</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>264,000 DoorDash drivers are getting money in a massive $131.5 million settlement. Here’s what happened</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNY2ozcHhYMTlTRkZnMmdzdjVjV1R0UnFZLUZGbEdmUDljVGxIVmd0VnNkS2lhZlZSZ3RCS29RR3FVV0xva01aQ2s4WWZlbEZMT1IwUWQxYzUzQlpyNmQ2Y2NESlA1djkyT2J2dE9zcWhHRHl4Y2NyTldzb1ZxaFM5amlMWmUyY1R1dXJ0RkQyN0Utd2FfQ0pDbEdOM0xJOUEyWEVvRTNvTlNveUdsbEp3Wjd3dVd3bV9aMkRFVm1QUTBjcmpOU3IwazNCR0Rmd3hwMHc?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Fast Company</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>7f008e57229c4525928c23566a502bf7</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>2e3cbf412e6b971f409ab631</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>359cb2ef8d9e53fd6bea742b</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.018</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQb1NHOHlpTmZEYVlXN0JHWGtqR29BQ1YtbVJBNWcyZUthSG92NmtEaDM0bjN4U0xJU2o1aDZCRTR6dXZ6TWpSSjg2aHB6V1VFck1JUUY5ZWlSb2FMcFB1amFIYnM3T2dmSnk0WGFuWm8tak1YV1M0aV9uZDVUMFVMQ3dDMVgtYXJr?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>WBAY</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>70ff7aa43f371daf788dc183</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>8eb8de929f0d100c02257b4c</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG3" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3838,12 +3974,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -3853,7 +3989,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>NYC Mayor Mamdani reaches record DoorDash settlement for underpaid workers</t>
+          <t>Paramount Shares Tick Up After Settlement As Wall Street Remains Cautiously Optimistic About WBD Merger</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -3864,7 +4000,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3894,7 +4030,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
@@ -3908,12 +4044,12 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPWXg3QnpvYVRxbXBDX1hjWmxFRjBiQUhvaVJ0VTBOaU9EdGFsT1ZtSzd2ZmNDN2pPempDTzhFTWM3YmRzekZvS1NfWk5DN1hVcUkzaFpuOGdZdXJPdVRIbkhORUdJNHdOcVZuUF81by1PYVNKSEprbmVxekwzWW85RzNBVW5SUENUUXIzOVhJYU96QnpkS2dyX19xUFRrUEJaLW42a09ES2dHUXJ4b1c3SFJYTUEwOFgyT2fSAb8BQVVfeXFMTnVzS0dCSlJxTHppRHk0NXNac3NneVZwTm14eVJvWElySlg5YlBmcjhQOGh0dHJwTVdaeGJOSFF1Z2VPUHE3VVd6SDViSy1ad00zcWVhbHY4S1FfVTJXNTc4Y3pQcDBDR2JYMnc0N1dNNE1Cc0x5MDhSSUZXeU5SMFM5cjZCcEFPdWZuc19nT3pUcEVQYUswdUFUQmhFbURhcV96LXF6Wk9zRjNTZlJjR0FvTXY0XzVCOEltZk53REE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNdlpNNl9aZ3FjTkJtbjJVYU1GbkRIdF9SYS02YUt5S1V2TDlGU1ZHR2NabDRFalY1U3p3OEhOVldlYUdnLUZWMVQxVTJNOTlCc19FaUd4cU5lNVNla0RNS29oYnNwVGxLUWdSblFhOG5BdXNwMW5jLUdIM0hhekRGb0RGd2gydw?oc=5</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr"/>
@@ -3924,7 +4060,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -3935,17 +4071,17 @@
       <c r="AA4" s="3" t="inlineStr"/>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>ed664f6928a140bb8e80fc7a5389dd9f</t>
+          <t>c011730a15f745b8addec9569a85b937</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>ee35c0a5a1eabe2b10ed79fc</t>
+          <t>cfb78cadb9c95baa99c80188</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>401e1cc6f638d8d5292d8f4f</t>
+          <t>99e4ec3be3ff19a9de617695</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr"/>
@@ -3970,18 +4106,14 @@
       <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="inlineStr"/>
       <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW4" s="3" t="inlineStr"/>
       <c r="AX4" s="3" t="inlineStr"/>
       <c r="AY4" s="3" t="inlineStr"/>
       <c r="AZ4" s="3" t="inlineStr"/>
       <c r="BA4" s="3" t="inlineStr"/>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="BC4" s="3" t="inlineStr">
@@ -3992,21 +4124,21 @@
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr"/>
       <c r="BG4" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="3" t="inlineStr"/>
       <c r="BK4" s="3" t="inlineStr">
         <is>
@@ -4020,344 +4152,392 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Cooper Companies (The)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>DoorDash, Inc.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>2026-09-22T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Brewers COO previews playoffs, ticket sales, fan rally</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>DoorDash reaches $131.5M settlement with New York City over delivery workers’ pay</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>'-0.835</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPQVUzV0tOT1pWUThjMmFEdjJXMmM0dHkteHpmWU00Yk90N013RXRQdWVzUEVENW5qQmhwdk1UNDlyVXljY1dTUDhobVhZTldLN1kxZ3RrSVQzbHQ4NmhkdTZOeGdqbmhid0pBdlpQLXNsVDJsS3NudzBPcVBDaXB5aXBZQ0drQTRpci1uQlluT01ES1k?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>NBC News</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>abf29ab2ecee42809099d56ada0c02fa</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>e0fed90d886dafd33a7a6572</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>3bb0fc363ada1398d012ae4f</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNdHFXSkE4ZDJpdkVUQVpTVkk1YkZ2MTcxcHhVWEVHSEJzRmMzbkRPYXAtc3Nha2VUM2lHcXdEMGtIWkpBZnpJVlpZQ2Ixc0VPZWxRankwZG5zZFZsNHZ2S2ZhN1BrZWJjNWlIelJvMUUtamtMcG1kNWt3VXJnR2xjbEV2Um15QzRMVVhUQjh30gGiAUFVX3lxTE9aRVZHLWoteTMzbFN3NFAtc3J4T2VfVmNqTjlWVmkwVG84blJMc3RNX1lURndXT2RuWDlNWHNqcjZsbElOdWxpcktldE1yX0NyWVE4OV9RY3F0WEhrMDY5VXRicUNfX1Z0VjZYQUxJQTdFNTlLaWctc2V0WXgxSW1EaXh1Nm9zTzJIc3lZUlg4cUdtNnhsc29FNnJNalk0WEI5QQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>WBAY</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>e674416ebd46d3b83ff64ddc</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>d953221ef41ef6b8d6a991df</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr"/>
-      <c r="BG5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
-      <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>AZO</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>AutoZone, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>DoorDash, Inc.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-09-22T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>AutoZone Climbs 6% as Profit Beat Offsets Revenue Miss; Advance Auto Parts Rises 6%, O'Reilly Automotive Gains 4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>DoorDash reaches $131.5M settlement with NYC over courier pay</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>'-0.471</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMk1jaVJ3T01DSFRLdGNPZjVwQnNOcVVDUV9QblluOVcyVWYzaTZReVZfY2NpMHM4Uy03T2wwZWJIQlhFQkw0cnlIbmp4aUdEVTc0VHVsakNkV1JlR2tTazd1cUhldTBob0hlQ2p6LWVfdUpnay03LWtEUTUtOVhDbnFvN0d0MHdZZ25pd09tdUxUaVQzbDYxaHF5cVlqdExjTkhmZg?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Nation’s Restaurant News</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>8f5394e3189146e8ac157d4d8e75852c</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>143c6de813c9ecade1e5f544</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>20e866e6ff1e8f2a0b75463b</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.895</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPRk94eHFhZlB0bFhDX21BR0I3YU1aekNMQnNZOTRNUDVYb1F6QnBNMVhrUVhaRU9SY3R2THFoRVRRZ2hFdE1QM0tPN1NFYkdmS1AzTkVXbTFmY2RfUzE2UWNpRmhyb2N1N2pILWJFeDFFV0VDOFp3WDg4amFkVF85UExzU3RtaHh3U2daNFBwdENvYWRTMFBhZGNxTHJnS1NLY3hVMkxNWTVTMnRDaVlDU0Raa085bllTRURqaWF5cGMwdWZZWVNOOEp4dHlGbV9peXBRU2RJcXhuU2ItdndPVm1FelNVdw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>24/7 Wall St.</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>revenue miss</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>9877d4441ca0e3d1efc7e8cc</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>1a0377ef33f45dfd169e6928</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>AZO</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4372,12 +4552,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -4387,7 +4567,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>264,000 DoorDash drivers are getting money in a massive $131.5 million settlement. Here’s what happened</t>
+          <t>Paramount-WBD Hearing Date Set For Proposed AGs Settlement</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -4398,7 +4578,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -4428,7 +4608,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>'-0.079</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr"/>
@@ -4442,12 +4622,12 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNY2ozcHhYMTlTRkZnMmdzdjVjV1R0UnFZLUZGbEdmUDljVGxIVmd0VnNkS2lhZlZSZ3RCS29RR3FVV0xva01aQ2s4WWZlbEZMT1IwUWQxYzUzQlpyNmQ2Y2NESlA1djkyT2J2dE9zcWhHRHl4Y2NyTldzb1ZxaFM5amlMWmUyY1R1dXJ0RkQyN0Utd2FfQ0pDbEdOM0xJOUEyWEVvRTNvTlNveUdsbEp3Wjd3dVd3bV9aMkRFVm1QUTBjcmpOU3IwazNCR0Rmd3hwMHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPcUp1d3hWblFjbEJYejZrV2hsaElWbHRNWGY1OFk5OWFYRFVYN18yMkt4U1pLaTRiNU9uVnlSbjhzZHQ0c0lIaXFHcm1rdVhoU09KaGlkS29CRWY1bXRSRFliM3VlMDliZ0h5REZkR2VnY2dBaGxiOEVFam56Nm1NTE41SThfQl9p?oc=5</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Fast Company</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr"/>
@@ -4458,7 +4638,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -4469,17 +4649,17 @@
       <c r="AA7" s="3" t="inlineStr"/>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>7f008e57229c4525928c23566a502bf7</t>
+          <t>ce0f0fbadacd4f46a2d22c6f53ff87f4</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>2e3cbf412e6b971f409ab631</t>
+          <t>0fad036315354fe89194f745</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>359cb2ef8d9e53fd6bea742b</t>
+          <t>29a31dd209b460e19931d92b</t>
         </is>
       </c>
       <c r="AE7" s="3" t="inlineStr"/>
@@ -4504,18 +4684,14 @@
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
       <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW7" s="3" t="inlineStr"/>
       <c r="AX7" s="3" t="inlineStr"/>
       <c r="AY7" s="3" t="inlineStr"/>
       <c r="AZ7" s="3" t="inlineStr"/>
       <c r="BA7" s="3" t="inlineStr"/>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="BC7" s="3" t="inlineStr">
@@ -4526,21 +4702,21 @@
       <c r="BD7" s="3" t="inlineStr"/>
       <c r="BE7" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="3" t="inlineStr"/>
       <c r="BG7" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="3" t="inlineStr"/>
       <c r="BK7" s="3" t="inlineStr">
         <is>
@@ -4566,12 +4742,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4581,7 +4757,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Paramount Shares Tick Up After Settlement As Wall Street Remains Cautiously Optimistic About WBD Merger</t>
+          <t>DoorDash Agrees to $131.5 Million Settlement for Shortchanging Workers</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -4592,7 +4768,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>反壟斷調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -4622,7 +4798,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>'-0.017</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr"/>
@@ -4636,12 +4812,12 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNdlpNNl9aZ3FjTkJtbjJVYU1GbkRIdF9SYS02YUt5S1V2TDlGU1ZHR2NabDRFalY1U3p3OEhOVldlYUdnLUZWMVQxVTJNOTlCc19FaUd4cU5lNVNla0RNS29oYnNwVGxLUWdSblFhOG5BdXNwMW5jLUdIM0hhekRGb0RGd2gydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQX1lPRUYwa2hCaU56ZzNBaUZvQ0hvTHNONEx0OWxSdnQwTXRDd2dOeWZXbWl2TkhvWjNaYWE2Q2FQb0QwRy1LZk41MUktLW5ZMVlVRVBhUjR4X1Q2M3N0T1BNdzhLWmNXNk05RXpYQ1FmVVdJQTlDSFZuX21SNTNnLVNjYWt1VTJ6dkhvaDNR?oc=5</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr"/>
@@ -4652,7 +4828,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>ANTITRUST_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -4663,17 +4839,17 @@
       <c r="AA8" s="3" t="inlineStr"/>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>c011730a15f745b8addec9569a85b937</t>
+          <t>0d2431f5e410458888841bf071fcc8e5</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>cfb78cadb9c95baa99c80188</t>
+          <t>45cd1b814114d1e9bad0217b</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>99e4ec3be3ff19a9de617695</t>
+          <t>e43fd33fff45d35320eff26a</t>
         </is>
       </c>
       <c r="AE8" s="3" t="inlineStr"/>
@@ -4698,14 +4874,18 @@
       <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="inlineStr"/>
       <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX8" s="3" t="inlineStr"/>
       <c r="AY8" s="3" t="inlineStr"/>
       <c r="AZ8" s="3" t="inlineStr"/>
       <c r="BA8" s="3" t="inlineStr"/>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="BC8" s="3" t="inlineStr">
@@ -4716,21 +4896,21 @@
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG8" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
+      <c r="BI8" s="3" t="inlineStr"/>
       <c r="BJ8" s="3" t="inlineStr"/>
       <c r="BK8" s="3" t="inlineStr">
         <is>
@@ -4743,780 +4923,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash, Inc.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash reaches $131.5M settlement with New York City over delivery workers’ pay</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.835</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPQVUzV0tOT1pWUThjMmFEdjJXMmM0dHkteHpmWU00Yk90N013RXRQdWVzUEVENW5qQmhwdk1UNDlyVXljY1dTUDhobVhZTldLN1kxZ3RrSVQzbHQ4NmhkdTZOeGdqbmhid0pBdlpQLXNsVDJsS3NudzBPcVBDaXB5aXBZQ0drQTRpci1uQlluT01ES1k?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>NBC News</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>abf29ab2ecee42809099d56ada0c02fa</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>e0fed90d886dafd33a7a6572</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>3bb0fc363ada1398d012ae4f</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash, Inc.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash reaches $131.5M settlement with NYC over courier pay</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>'-0.471</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMk1jaVJ3T01DSFRLdGNPZjVwQnNOcVVDUV9QblluOVcyVWYzaTZReVZfY2NpMHM4Uy03T2wwZWJIQlhFQkw0cnlIbmp4aUdEVTc0VHVsakNkV1JlR2tTazd1cUhldTBob0hlQ2p6LWVfdUpnay03LWtEUTUtOVhDbnFvN0d0MHdZZ25pd09tdUxUaVQzbDYxaHF5cVlqdExjTkhmZg?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Nation’s Restaurant News</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr">
-        <is>
-          <t>8f5394e3189146e8ac157d4d8e75852c</t>
-        </is>
-      </c>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>143c6de813c9ecade1e5f544</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>20e866e6ff1e8f2a0b75463b</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="BC10" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Paramount-WBD Hearing Date Set For Proposed AGs Settlement</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.079</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPcUp1d3hWblFjbEJYejZrV2hsaElWbHRNWGY1OFk5OWFYRFVYN18yMkt4U1pLaTRiNU9uVnlSbjhzZHQ0c0lIaXFHcm1rdVhoU09KaGlkS29CRWY1bXRSRFliM3VlMDliZ0h5REZkR2VnY2dBaGxiOEVFam56Nm1NTE41SThfQl9p?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>ce0f0fbadacd4f46a2d22c6f53ff87f4</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>0fad036315354fe89194f745</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>29a31dd209b460e19931d92b</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr"/>
-      <c r="BG11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash, Inc.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>DoorDash Agrees to $131.5 Million Settlement for Shortchanging Workers</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>'-0.017</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQX1lPRUYwa2hCaU56ZzNBaUZvQ0hvTHNONEx0OWxSdnQwTXRDd2dOeWZXbWl2TkhvWjNaYWE2Q2FQb0QwRy1LZk41MUktLW5ZMVlVRVBhUjR4X1Q2M3N0T1BNdzhLWmNXNk05RXpYQ1FmVVdJQTlDSFZuX21SNTNnLVNjYWt1VTJ6dkhvaDNR?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>The New York Times</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr">
-        <is>
-          <t>0d2431f5e410458888841bf071fcc8e5</t>
-        </is>
-      </c>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>45cd1b814114d1e9bad0217b</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>e43fd33fff45d35320eff26a</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL12"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6503,645 +5911,645 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-26</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H2" s="4" t="b">
+      <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:23:38.366332+08:00</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:40:53.776257+08:00</t>
         </is>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="2" t="n">
         <v>1926</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1976</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
         </is>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-25</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:23:17.137147+08:00</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:40:12.120180+08:00</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="2" t="n">
         <v>2032</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2089</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
         </is>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W3" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-24</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H4" s="4" t="b">
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T12:44:09.884829+08:00</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T13:04:34.984103+08:00</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="2" t="n">
         <v>3760</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3802</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="2" t="n">
         <v>3825</v>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
         </is>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="2" t="n">
         <v>3793</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="W4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296780+08:00</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296790+08:00</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="n">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
         <v>1691</v>
       </c>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="n">
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="Y5" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-10-22T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="b">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:34.299718+08:00</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:32:11.776786+08:00</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="W6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H7" s="4" t="b">
+      <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="Q7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="R7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="V7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="W7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H8" s="4" t="b">
+      <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA8"/>
